--- a/artfynd/A 57390-2023 artfynd.xlsx
+++ b/artfynd/A 57390-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57390-2023 artfynd.xlsx
+++ b/artfynd/A 57390-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95662440</v>
+        <v>104563233</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strömsund, Jmt</t>
+          <t>Håxåskälen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512525.8980689218</v>
+        <v>512363</v>
       </c>
       <c r="R2" t="n">
-        <v>7045780.043236898</v>
+        <v>7045639</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,68 +765,67 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Olikåldrig barrblandskog på frisk mark med med lågört, tidigare luckhugget</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95662453</v>
+        <v>95662388</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512524.5108913276</v>
+        <v>512466</v>
       </c>
       <c r="R3" t="n">
-        <v>7045792.079810277</v>
+        <v>7045793</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +855,9 @@
           <t>2021-08-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,52 +884,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95662640</v>
+        <v>95662397</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512481.2454044305</v>
+        <v>512467</v>
       </c>
       <c r="R4" t="n">
-        <v>7045664.351130663</v>
+        <v>7045784</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,19 +953,9 @@
           <t>2021-08-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,52 +982,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95662418</v>
+        <v>95662410</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Strömsund, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512481.725706049</v>
+        <v>512481</v>
       </c>
       <c r="R5" t="n">
-        <v>7045769.61157986</v>
+        <v>7045796</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1092,19 +1051,9 @@
           <t>2021-08-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,55 +1080,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101886141</v>
+        <v>107270860</v>
       </c>
       <c r="B6" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strömsund, Jmt</t>
+          <t>Håxåskälen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512518.2647505956</v>
+        <v>512125</v>
       </c>
       <c r="R6" t="n">
-        <v>7045676.98504563</v>
+        <v>7045539</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,22 +1145,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-06-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-06-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,15 +1165,613 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>95599761</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>512143</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7045537</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>95662418</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>512482</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7045769</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-08-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-08-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>95662440</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>512526</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7045780</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-08-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-08-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>95662453</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>512525</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7045792</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-08-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-08-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>95662640</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>512481</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7045665</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-08-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-08-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>101886141</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>512518</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7045677</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-06-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-06-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57390-2023 artfynd.xlsx
+++ b/artfynd/A 57390-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563233</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95662388</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95662397</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95662410</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107270860</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1277,6 +1307,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95599761</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95662418</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1475,6 +1515,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95662440</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1574,6 +1619,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95662453</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1673,6 +1723,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95662640</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1772,8 +1827,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101886141</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>